--- a/diseases/d131/2015-2019.xlsx
+++ b/diseases/d131/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2698,6 +2763,11 @@
       <c r="S15" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">

--- a/diseases/d131/2015-2019.xlsx
+++ b/diseases/d131/2015-2019.xlsx
@@ -765,17 +765,15 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -788,23 +786,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -918,17 +906,15 @@
       <c r="O3" t="n">
         <v>1</v>
       </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -941,23 +927,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1071,17 +1047,15 @@
       <c r="O4" t="n">
         <v>2</v>
       </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.0005920837225093475</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1094,23 +1068,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1224,17 +1188,15 @@
       <c r="O5" t="n">
         <v>2</v>
       </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.0005920837225093475</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1247,23 +1209,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1377,17 +1329,15 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.0005920837225093475</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1400,23 +1350,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1530,17 +1470,15 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1553,23 +1491,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1683,17 +1611,15 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1706,23 +1632,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1836,17 +1752,15 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1859,23 +1773,13 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1989,17 +1893,15 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2012,23 +1914,13 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2142,17 +2034,15 @@
       <c r="O11" t="n">
         <v>1</v>
       </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2165,23 +2055,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2295,17 +2175,15 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2318,23 +2196,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2448,17 +2316,15 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2471,23 +2337,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2601,17 +2457,15 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2624,23 +2478,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2754,17 +2598,15 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2777,22 +2619,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
